--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/106.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/106.xlsx
@@ -426,13 +426,13 @@
         <v>-16.51438495347005</v>
       </c>
       <c r="E2">
-        <v>-3.785570866471622</v>
+        <v>-7.957409432141908</v>
       </c>
       <c r="F2">
-        <v>-3.535681114660852</v>
+        <v>-3.755520875753705</v>
       </c>
       <c r="G2">
-        <v>-12.25952731751337</v>
+        <v>-13.64847331960568</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.92361302293201</v>
       </c>
       <c r="E3">
-        <v>-4.225344562778513</v>
+        <v>-8.053299869254328</v>
       </c>
       <c r="F3">
-        <v>-3.533547070939797</v>
+        <v>-3.463724644539902</v>
       </c>
       <c r="G3">
-        <v>-12.41621212734154</v>
+        <v>-12.94858757660282</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.35682824770705</v>
       </c>
       <c r="E4">
-        <v>-5.032051450978918</v>
+        <v>-6.443323204625339</v>
       </c>
       <c r="F4">
-        <v>-3.36486338647451</v>
+        <v>-3.587959246929508</v>
       </c>
       <c r="G4">
-        <v>-12.21456017745345</v>
+        <v>-13.52887158563566</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.90223189524595</v>
       </c>
       <c r="E5">
-        <v>-5.489776018252215</v>
+        <v>-8.118704619347112</v>
       </c>
       <c r="F5">
-        <v>-3.323955470825752</v>
+        <v>-3.325250150411624</v>
       </c>
       <c r="G5">
-        <v>-11.64797355058935</v>
+        <v>-12.90216379650562</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.52260275294846</v>
       </c>
       <c r="E6">
-        <v>-5.659675306071992</v>
+        <v>-10.30495224382219</v>
       </c>
       <c r="F6">
-        <v>-2.946910725742717</v>
+        <v>-3.342438902564846</v>
       </c>
       <c r="G6">
-        <v>-12.09571159259362</v>
+        <v>-14.42442546746437</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.20762789022094</v>
       </c>
       <c r="E7">
-        <v>-8.774228402801441</v>
+        <v>-10.36559756773291</v>
       </c>
       <c r="F7">
-        <v>-3.249806359864877</v>
+        <v>-3.041808759754722</v>
       </c>
       <c r="G7">
-        <v>-12.47522591212459</v>
+        <v>-13.40813433454567</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.9165631785342</v>
       </c>
       <c r="E8">
-        <v>-8.451425190112674</v>
+        <v>-12.57590950308475</v>
       </c>
       <c r="F8">
-        <v>-2.730764958697625</v>
+        <v>-2.59637642583118</v>
       </c>
       <c r="G8">
-        <v>-11.39705406198583</v>
+        <v>-13.55591046632765</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.60583953229917</v>
       </c>
       <c r="E9">
-        <v>-8.654998210653488</v>
+        <v>-13.02822707239289</v>
       </c>
       <c r="F9">
-        <v>-2.711312298938283</v>
+        <v>-3.048801613224345</v>
       </c>
       <c r="G9">
-        <v>-12.19646142499026</v>
+        <v>-12.88286000546613</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.24130835223702</v>
       </c>
       <c r="E10">
-        <v>-11.8883739368702</v>
+        <v>-13.58862120236809</v>
       </c>
       <c r="F10">
-        <v>-2.554439101337386</v>
+        <v>-2.665834599870524</v>
       </c>
       <c r="G10">
-        <v>-11.9591449680076</v>
+        <v>-13.8148530620456</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.77967557136809</v>
       </c>
       <c r="E11">
-        <v>-12.15391006725797</v>
+        <v>-13.13711875838133</v>
       </c>
       <c r="F11">
-        <v>-2.096489155858211</v>
+        <v>-2.930402967133134</v>
       </c>
       <c r="G11">
-        <v>-10.67635160863203</v>
+        <v>-12.13602741617086</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.2071323785021</v>
       </c>
       <c r="E12">
-        <v>-12.39866503042454</v>
+        <v>-16.78783412067094</v>
       </c>
       <c r="F12">
-        <v>-2.289534988420703</v>
+        <v>-2.735033046139735</v>
       </c>
       <c r="G12">
-        <v>-10.78885387769308</v>
+        <v>-11.87479888875805</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.49877486505427</v>
       </c>
       <c r="E13">
-        <v>-12.91114790539858</v>
+        <v>-15.8838691962078</v>
       </c>
       <c r="F13">
-        <v>-2.344974989549534</v>
+        <v>-2.715629481263771</v>
       </c>
       <c r="G13">
-        <v>-11.0602325377293</v>
+        <v>-13.45374703098575</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.66700944713655</v>
       </c>
       <c r="E14">
-        <v>-14.80981478801655</v>
+        <v>-16.90882588920787</v>
       </c>
       <c r="F14">
-        <v>-2.383422618058658</v>
+        <v>-2.945007111232358</v>
       </c>
       <c r="G14">
-        <v>-10.23206315507968</v>
+        <v>-12.40688963110295</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.724926409207583</v>
       </c>
       <c r="E15">
-        <v>-15.07915936504477</v>
+        <v>-16.2787793005207</v>
       </c>
       <c r="F15">
-        <v>-2.046079004716816</v>
+        <v>-2.196360026444696</v>
       </c>
       <c r="G15">
-        <v>-9.608478865665939</v>
+        <v>-9.900836452784516</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.705287716750213</v>
       </c>
       <c r="E16">
-        <v>-16.69045381560999</v>
+        <v>-18.58118228329252</v>
       </c>
       <c r="F16">
-        <v>-1.529609541956238</v>
+        <v>-1.920325628354304</v>
       </c>
       <c r="G16">
-        <v>-9.537878171495441</v>
+        <v>-9.768010744657877</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.656056524673963</v>
       </c>
       <c r="E17">
-        <v>-18.13965153907065</v>
+        <v>-20.33141031641307</v>
       </c>
       <c r="F17">
-        <v>-1.926485452512406</v>
+        <v>-2.188063783006667</v>
       </c>
       <c r="G17">
-        <v>-7.751610425416426</v>
+        <v>-9.502041516032831</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.621432829674996</v>
       </c>
       <c r="E18">
-        <v>-18.96541424589534</v>
+        <v>-19.28091755848374</v>
       </c>
       <c r="F18">
-        <v>-1.235941370350386</v>
+        <v>-2.040657979368267</v>
       </c>
       <c r="G18">
-        <v>-7.352706240661944</v>
+        <v>-8.568762312511351</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.662477784207693</v>
       </c>
       <c r="E19">
-        <v>-19.80972105378143</v>
+        <v>-21.03184297660146</v>
       </c>
       <c r="F19">
-        <v>-1.337494928472025</v>
+        <v>-2.235659688736326</v>
       </c>
       <c r="G19">
-        <v>-6.774824032417844</v>
+        <v>-8.771642474794506</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.816849033895964</v>
       </c>
       <c r="E20">
-        <v>-20.59176134406205</v>
+        <v>-21.80764755817353</v>
       </c>
       <c r="F20">
-        <v>-1.265694453383747</v>
+        <v>-1.69237412556257</v>
       </c>
       <c r="G20">
-        <v>-5.5761979828327</v>
+        <v>-7.958072597973073</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.133178112647166</v>
       </c>
       <c r="E21">
-        <v>-21.22467445679608</v>
+        <v>-23.02437606845043</v>
       </c>
       <c r="F21">
-        <v>-1.262546046023854</v>
+        <v>-1.731658742648003</v>
       </c>
       <c r="G21">
-        <v>-4.978369737714492</v>
+        <v>-8.017986851142803</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.633346189170859</v>
       </c>
       <c r="E22">
-        <v>-23.0504555502606</v>
+        <v>-23.7475235542613</v>
       </c>
       <c r="F22">
-        <v>-0.9241009652178241</v>
+        <v>-1.48589213201349</v>
       </c>
       <c r="G22">
-        <v>-4.342367591982947</v>
+        <v>-6.531637978194062</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.333827858151451</v>
       </c>
       <c r="E23">
-        <v>-23.05871548685059</v>
+        <v>-24.81345388008278</v>
       </c>
       <c r="F23">
-        <v>-1.083089993921748</v>
+        <v>-0.7017692428670265</v>
       </c>
       <c r="G23">
-        <v>-4.6907065041706</v>
+        <v>-6.922477674014878</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.23346105744596</v>
       </c>
       <c r="E24">
-        <v>-23.1353508524824</v>
+        <v>-25.18067689431279</v>
       </c>
       <c r="F24">
-        <v>-0.5201648936906272</v>
+        <v>-1.136467218095719</v>
       </c>
       <c r="G24">
-        <v>-4.503114441187798</v>
+        <v>-6.243196766448441</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.306966789843563</v>
       </c>
       <c r="E25">
-        <v>-23.79440231718871</v>
+        <v>-25.42864254555079</v>
       </c>
       <c r="F25">
-        <v>-0.9552445420449409</v>
+        <v>-0.8275645874362972</v>
       </c>
       <c r="G25">
-        <v>-3.806429995721413</v>
+        <v>-6.104322691621554</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.523593604154251</v>
       </c>
       <c r="E26">
-        <v>-25.06864697583703</v>
+        <v>-25.45202305685239</v>
       </c>
       <c r="F26">
-        <v>-0.8460139694982091</v>
+        <v>-1.234410718583114</v>
       </c>
       <c r="G26">
-        <v>-4.708782082815021</v>
+        <v>-7.504041208898648</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.82777151306389</v>
       </c>
       <c r="E27">
-        <v>-22.96480399287953</v>
+        <v>-24.84188363990294</v>
       </c>
       <c r="F27">
-        <v>-0.5106016855202462</v>
+        <v>0.1470258610423226</v>
       </c>
       <c r="G27">
-        <v>-4.087247021090091</v>
+        <v>-6.351663480497122</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.172122813244856</v>
       </c>
       <c r="E28">
-        <v>-24.11126870045342</v>
+        <v>-25.4667858821174</v>
       </c>
       <c r="F28">
-        <v>-0.9960518923680691</v>
+        <v>-0.8592949273050843</v>
       </c>
       <c r="G28">
-        <v>-4.198385345388965</v>
+        <v>-6.436830575040413</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.497792312504924</v>
       </c>
       <c r="E29">
-        <v>-23.53937224649873</v>
+        <v>-27.15496023591084</v>
       </c>
       <c r="F29">
-        <v>-0.9169734967453889</v>
+        <v>-0.6952776323196401</v>
       </c>
       <c r="G29">
-        <v>-4.772814654635604</v>
+        <v>-7.949435384661115</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.759518788225351</v>
       </c>
       <c r="E30">
-        <v>-23.86989197889657</v>
+        <v>-25.22357965706145</v>
       </c>
       <c r="F30">
-        <v>-0.9856303155915198</v>
+        <v>-0.6482732407493973</v>
       </c>
       <c r="G30">
-        <v>-5.527446889221393</v>
+        <v>-7.106686359456545</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.917107874915279</v>
       </c>
       <c r="E31">
-        <v>-23.74180409158961</v>
+        <v>-25.62966150675128</v>
       </c>
       <c r="F31">
-        <v>-1.056262015714204</v>
+        <v>-1.005125735410579</v>
       </c>
       <c r="G31">
-        <v>-4.942572808798352</v>
+        <v>-7.946916059505729</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.944411991128624</v>
       </c>
       <c r="E32">
-        <v>-24.61946763901621</v>
+        <v>-24.7560192442435</v>
       </c>
       <c r="F32">
-        <v>-0.9194630824444597</v>
+        <v>-0.4138111229392912</v>
       </c>
       <c r="G32">
-        <v>-5.141059877150895</v>
+        <v>-7.07622602994971</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.833542850030482</v>
       </c>
       <c r="E33">
-        <v>-23.68009004781308</v>
+        <v>-24.010655064951</v>
       </c>
       <c r="F33">
-        <v>-1.154034475962731</v>
+        <v>-1.387887658848351</v>
       </c>
       <c r="G33">
-        <v>-5.142010003720666</v>
+        <v>-6.876699450297837</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.588412410635588</v>
       </c>
       <c r="E34">
-        <v>-23.12665165391367</v>
+        <v>-25.57863466163285</v>
       </c>
       <c r="F34">
-        <v>-1.22738698284814</v>
+        <v>-0.8996762607369593</v>
       </c>
       <c r="G34">
-        <v>-4.42411489298417</v>
+        <v>-7.878645989394879</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.230892722010099</v>
       </c>
       <c r="E35">
-        <v>-22.75596435706779</v>
+        <v>-24.92303389412039</v>
       </c>
       <c r="F35">
-        <v>-1.221451253077073</v>
+        <v>-0.8518942695622357</v>
       </c>
       <c r="G35">
-        <v>-3.924424459832117</v>
+        <v>-6.84075023628689</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.787657970342696</v>
       </c>
       <c r="E36">
-        <v>-21.92265721254633</v>
+        <v>-25.04796090656999</v>
       </c>
       <c r="F36">
-        <v>-0.5768607736104018</v>
+        <v>-1.267339923829889</v>
       </c>
       <c r="G36">
-        <v>-3.940824902433666</v>
+        <v>-7.76876236185539</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.296382043479827</v>
       </c>
       <c r="E37">
-        <v>-23.24285682542449</v>
+        <v>-23.81036518806574</v>
       </c>
       <c r="F37">
-        <v>-1.149679284695273</v>
+        <v>-0.841973935707923</v>
       </c>
       <c r="G37">
-        <v>-5.04505736705757</v>
+        <v>-6.767593800960076</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.794092702713848</v>
       </c>
       <c r="E38">
-        <v>-21.62891774603879</v>
+        <v>-23.49403769320795</v>
       </c>
       <c r="F38">
-        <v>-1.129331039240749</v>
+        <v>-1.118008333798315</v>
       </c>
       <c r="G38">
-        <v>-4.352762704976258</v>
+        <v>-7.101164369497041</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.317807158481202</v>
       </c>
       <c r="E39">
-        <v>-20.64762007094667</v>
+        <v>-23.00130802185536</v>
       </c>
       <c r="F39">
-        <v>-1.038047022127777</v>
+        <v>-0.8112928010081146</v>
       </c>
       <c r="G39">
-        <v>-5.043888744482207</v>
+        <v>-7.391628324567155</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.901044166971326</v>
       </c>
       <c r="E40">
-        <v>-20.08353070618121</v>
+        <v>-23.1999993474159</v>
       </c>
       <c r="F40">
-        <v>-0.5672294660856568</v>
+        <v>-0.3117365255714725</v>
       </c>
       <c r="G40">
-        <v>-4.515111858222117</v>
+        <v>-7.437823677022146</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.565101844563919</v>
       </c>
       <c r="E41">
-        <v>-19.00916836175745</v>
+        <v>-22.35679295871367</v>
       </c>
       <c r="F41">
-        <v>-0.9651292425161562</v>
+        <v>-0.9634687268638179</v>
       </c>
       <c r="G41">
-        <v>-4.455111530868367</v>
+        <v>-7.189675115034995</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.329176172139408</v>
       </c>
       <c r="E42">
-        <v>-19.3957234315262</v>
+        <v>-21.26960597590019</v>
       </c>
       <c r="F42">
-        <v>-0.7441761361647485</v>
+        <v>-0.7086955806882008</v>
       </c>
       <c r="G42">
-        <v>-4.818897448542259</v>
+        <v>-8.034609100295484</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.196802508279799</v>
       </c>
       <c r="E43">
-        <v>-18.2176092191127</v>
+        <v>-21.17996483291835</v>
       </c>
       <c r="F43">
-        <v>-1.065354071374742</v>
+        <v>-0.7617600229438727</v>
       </c>
       <c r="G43">
-        <v>-4.415570374947311</v>
+        <v>-7.335365603127242</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.171094714510741</v>
       </c>
       <c r="E44">
-        <v>-17.22694665977271</v>
+        <v>-20.48368478339499</v>
       </c>
       <c r="F44">
-        <v>-0.8287967106385091</v>
+        <v>-1.292851842421703</v>
       </c>
       <c r="G44">
-        <v>-4.367362210804444</v>
+        <v>-7.004311049200123</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.241649015078543</v>
       </c>
       <c r="E45">
-        <v>-18.42199283650088</v>
+        <v>-19.9947318593648</v>
       </c>
       <c r="F45">
-        <v>-0.7434310025315343</v>
+        <v>-0.5796132544914355</v>
       </c>
       <c r="G45">
-        <v>-4.769841784741339</v>
+        <v>-7.417963714332058</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.394639226556645</v>
       </c>
       <c r="E46">
-        <v>-17.51990722875093</v>
+        <v>-17.76644188220251</v>
       </c>
       <c r="F46">
-        <v>-1.237483899912024</v>
+        <v>-0.6624165264272294</v>
       </c>
       <c r="G46">
-        <v>-4.773642291020422</v>
+        <v>-7.317230434663114</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.612580673391315</v>
       </c>
       <c r="E47">
-        <v>-15.4605066897047</v>
+        <v>-19.11474067629826</v>
       </c>
       <c r="F47">
-        <v>-0.8862836516630456</v>
+        <v>-1.291006825030216</v>
       </c>
       <c r="G47">
-        <v>-4.85441298108756</v>
+        <v>-6.829590387274007</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.872486866736379</v>
       </c>
       <c r="E48">
-        <v>-15.30272559832945</v>
+        <v>-18.27999347704236</v>
       </c>
       <c r="F48">
-        <v>-0.8965246859652347</v>
+        <v>-1.25950533066621</v>
       </c>
       <c r="G48">
-        <v>-5.681774590625598</v>
+        <v>-8.270935704161896</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.159849614386824</v>
       </c>
       <c r="E49">
-        <v>-14.98829553408087</v>
+        <v>-17.33481038216141</v>
       </c>
       <c r="F49">
-        <v>-1.020511438379074</v>
+        <v>-0.9296914470993254</v>
       </c>
       <c r="G49">
-        <v>-5.328148737211728</v>
+        <v>-7.768596834578426</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.455571879824444</v>
       </c>
       <c r="E50">
-        <v>-14.82382588659629</v>
+        <v>-17.54701920263485</v>
       </c>
       <c r="F50">
-        <v>-1.123785692977838</v>
+        <v>-1.336049004971229</v>
       </c>
       <c r="G50">
-        <v>-5.772274974032654</v>
+        <v>-7.517220490690486</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.751962835923584</v>
       </c>
       <c r="E51">
-        <v>-12.60029986409006</v>
+        <v>-17.43528363496959</v>
       </c>
       <c r="F51">
-        <v>-1.12783047788587</v>
+        <v>-0.8217009162843826</v>
       </c>
       <c r="G51">
-        <v>-5.292692794486134</v>
+        <v>-7.59133367367815</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.04156078305293</v>
       </c>
       <c r="E52">
-        <v>-12.39686722624349</v>
+        <v>-16.41886764394798</v>
       </c>
       <c r="F52">
-        <v>-1.430849641069434</v>
+        <v>-0.9248033387913215</v>
       </c>
       <c r="G52">
-        <v>-5.400179587055191</v>
+        <v>-7.319097582347263</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.324497368795349</v>
       </c>
       <c r="E53">
-        <v>-12.91638282135145</v>
+        <v>-15.44854246137644</v>
       </c>
       <c r="F53">
-        <v>-1.237084806021334</v>
+        <v>-1.388841841662403</v>
       </c>
       <c r="G53">
-        <v>-6.202566441044966</v>
+        <v>-6.276000962197079</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.605906023030642</v>
       </c>
       <c r="E54">
-        <v>-12.57573742107246</v>
+        <v>-16.23579502523989</v>
       </c>
       <c r="F54">
-        <v>-1.107924086381754</v>
+        <v>-0.8543015025537036</v>
       </c>
       <c r="G54">
-        <v>-6.941182256311761</v>
+        <v>-7.793674217038405</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.887344835625719</v>
       </c>
       <c r="E55">
-        <v>-12.09876683926657</v>
+        <v>-16.21170354351908</v>
       </c>
       <c r="F55">
-        <v>-1.723297567267441</v>
+        <v>-1.248581719114466</v>
       </c>
       <c r="G55">
-        <v>-5.930194617346968</v>
+        <v>-7.016301845143363</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.178659232193811</v>
       </c>
       <c r="E56">
-        <v>-10.51470210290947</v>
+        <v>-14.4757990736848</v>
       </c>
       <c r="F56">
-        <v>-1.228503495518525</v>
+        <v>-1.350208919561173</v>
       </c>
       <c r="G56">
-        <v>-5.535286261058387</v>
+        <v>-8.03489380721186</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.478059373071376</v>
       </c>
       <c r="E57">
-        <v>-11.24295317892698</v>
+        <v>-13.90733520302793</v>
       </c>
       <c r="F57">
-        <v>-1.651369603852969</v>
+        <v>-1.794308564956872</v>
       </c>
       <c r="G57">
-        <v>-5.764985152755179</v>
+        <v>-8.252972684065812</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.789606232653399</v>
       </c>
       <c r="E58">
-        <v>-9.496755487673262</v>
+        <v>-14.46580926002388</v>
       </c>
       <c r="F58">
-        <v>-1.494847197112342</v>
+        <v>-1.432496695221491</v>
       </c>
       <c r="G58">
-        <v>-6.092490801864199</v>
+        <v>-7.637535647224219</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.107048681196223</v>
       </c>
       <c r="E59">
-        <v>-8.125814323539153</v>
+        <v>-12.22801854439349</v>
       </c>
       <c r="F59">
-        <v>-1.225054975887655</v>
+        <v>-1.337913026833701</v>
       </c>
       <c r="G59">
-        <v>-6.05428379579547</v>
+        <v>-7.851075766143828</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.426615124566587</v>
       </c>
       <c r="E60">
-        <v>-8.349960201496813</v>
+        <v>-12.983422350561</v>
       </c>
       <c r="F60">
-        <v>-1.789721360772802</v>
+        <v>-2.02119977663822</v>
       </c>
       <c r="G60">
-        <v>-6.527605733727229</v>
+        <v>-8.342446798355693</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.740294644336529</v>
       </c>
       <c r="E61">
-        <v>-8.44877150434418</v>
+        <v>-13.29305676083546</v>
       </c>
       <c r="F61">
-        <v>-1.516075191202893</v>
+        <v>-2.287393818023029</v>
       </c>
       <c r="G61">
-        <v>-6.2541943987299</v>
+        <v>-7.415004086619949</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.037389961914931</v>
       </c>
       <c r="E62">
-        <v>-7.850301964912489</v>
+        <v>-11.41321474466737</v>
       </c>
       <c r="F62">
-        <v>-1.569940196798819</v>
+        <v>-1.721130265722162</v>
       </c>
       <c r="G62">
-        <v>-6.417397672724891</v>
+        <v>-9.472782914556751</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.311566739564859</v>
       </c>
       <c r="E63">
-        <v>-7.749706443306099</v>
+        <v>-10.88155831074485</v>
       </c>
       <c r="F63">
-        <v>-1.807558640498396</v>
+        <v>-1.708049646713589</v>
       </c>
       <c r="G63">
-        <v>-6.733736851729949</v>
+        <v>-8.898916398051787</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.548162430771145</v>
       </c>
       <c r="E64">
-        <v>-6.504022870224153</v>
+        <v>-11.12930206675648</v>
       </c>
       <c r="F64">
-        <v>-1.508236638774425</v>
+        <v>-2.051155574028757</v>
       </c>
       <c r="G64">
-        <v>-7.828805726301151</v>
+        <v>-8.63517185602913</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.740280045608361</v>
       </c>
       <c r="E65">
-        <v>-7.2988877988945</v>
+        <v>-11.44539860943989</v>
       </c>
       <c r="F65">
-        <v>-1.796096568935403</v>
+        <v>-1.89016394919476</v>
       </c>
       <c r="G65">
-        <v>-7.504839050373612</v>
+        <v>-9.90785811987331</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.871721598459582</v>
       </c>
       <c r="E66">
-        <v>-6.287471243177357</v>
+        <v>-9.919221356322836</v>
       </c>
       <c r="F66">
-        <v>-1.810831368772652</v>
+        <v>-1.837355275444432</v>
       </c>
       <c r="G66">
-        <v>-7.56503801045972</v>
+        <v>-9.478728654345282</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.934004871580151</v>
       </c>
       <c r="E67">
-        <v>-5.485713977067335</v>
+        <v>-10.08160790576389</v>
       </c>
       <c r="F67">
-        <v>-2.224390829295017</v>
+        <v>-2.453119139838274</v>
       </c>
       <c r="G67">
-        <v>-7.740814736412863</v>
+        <v>-9.086131058843112</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.913304890616041</v>
       </c>
       <c r="E68">
-        <v>-7.187283556975464</v>
+        <v>-9.748425430649542</v>
       </c>
       <c r="F68">
-        <v>-2.159344859936088</v>
+        <v>-2.111893863297691</v>
       </c>
       <c r="G68">
-        <v>-8.303859079549948</v>
+        <v>-9.987648888460825</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.802751788777353</v>
       </c>
       <c r="E69">
-        <v>-6.071576244861672</v>
+        <v>-10.05633449232708</v>
       </c>
       <c r="F69">
-        <v>-1.959984000035781</v>
+        <v>-2.025426687726528</v>
       </c>
       <c r="G69">
-        <v>-8.4101904917258</v>
+        <v>-9.637843404599273</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.596912268220672</v>
       </c>
       <c r="E70">
-        <v>-6.144117869990543</v>
+        <v>-9.268846447815228</v>
       </c>
       <c r="F70">
-        <v>-2.500395928825973</v>
+        <v>-2.142499771966516</v>
       </c>
       <c r="G70">
-        <v>-7.527999626966353</v>
+        <v>-9.19011860477716</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.293501071371993</v>
       </c>
       <c r="E71">
-        <v>-6.510290278250769</v>
+        <v>-8.228502000137086</v>
       </c>
       <c r="F71">
-        <v>-2.494778523943909</v>
+        <v>-2.532248214050249</v>
       </c>
       <c r="G71">
-        <v>-8.282754351737095</v>
+        <v>-8.793041841160356</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.898887395453409</v>
       </c>
       <c r="E72">
-        <v>-5.629923231841597</v>
+        <v>-9.652172715616508</v>
       </c>
       <c r="F72">
-        <v>-2.474655164729378</v>
+        <v>-2.778217539041938</v>
       </c>
       <c r="G72">
-        <v>-7.567285870880885</v>
+        <v>-9.476149739370189</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.419250400388312</v>
       </c>
       <c r="E73">
-        <v>-7.010827038792581</v>
+        <v>-10.18356649804659</v>
       </c>
       <c r="F73">
-        <v>-2.691284753931636</v>
+        <v>-3.107751898514747</v>
       </c>
       <c r="G73">
-        <v>-7.457077809878546</v>
+        <v>-8.946909376734602</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.873344654145003</v>
       </c>
       <c r="E74">
-        <v>-5.351322453941702</v>
+        <v>-9.871079149147294</v>
       </c>
       <c r="F74">
-        <v>-2.157984456554725</v>
+        <v>-2.626481091577769</v>
       </c>
       <c r="G74">
-        <v>-7.592306974066696</v>
+        <v>-8.467870126656521</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.276254148122737</v>
       </c>
       <c r="E75">
-        <v>-5.767299019338285</v>
+        <v>-10.08203811079462</v>
       </c>
       <c r="F75">
-        <v>-2.903937657580225</v>
+        <v>-2.912293289990084</v>
       </c>
       <c r="G75">
-        <v>-7.444368625553285</v>
+        <v>-8.721782348427544</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.65590837542421</v>
       </c>
       <c r="E76">
-        <v>-6.689699361486653</v>
+        <v>-11.32311169733676</v>
       </c>
       <c r="F76">
-        <v>-2.784156436224836</v>
+        <v>-2.843866108501691</v>
       </c>
       <c r="G76">
-        <v>-7.772195397579614</v>
+        <v>-10.24050173565928</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.035233827429262</v>
       </c>
       <c r="E77">
-        <v>-7.682241237539826</v>
+        <v>-11.24460154346577</v>
       </c>
       <c r="F77">
-        <v>-2.787750656799926</v>
+        <v>-3.122133531932853</v>
       </c>
       <c r="G77">
-        <v>-7.753093549818019</v>
+        <v>-7.860206250741139</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.440274555067074</v>
       </c>
       <c r="E78">
-        <v>-8.175238088858867</v>
+        <v>-12.56359205378389</v>
       </c>
       <c r="F78">
-        <v>-2.687240760876561</v>
+        <v>-2.945059373527568</v>
       </c>
       <c r="G78">
-        <v>-7.35363319341294</v>
+        <v>-8.132372820615702</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.895069063052004</v>
       </c>
       <c r="E79">
-        <v>-8.491402558652389</v>
+        <v>-11.46641978578349</v>
       </c>
       <c r="F79">
-        <v>-3.248921860111104</v>
+        <v>-3.231061616649736</v>
       </c>
       <c r="G79">
-        <v>-7.050489848927417</v>
+        <v>-8.140271782272402</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.416170487794967</v>
       </c>
       <c r="E80">
-        <v>-8.758319873612495</v>
+        <v>-11.5141861296164</v>
       </c>
       <c r="F80">
-        <v>-3.308290243763182</v>
+        <v>-2.794970772068414</v>
       </c>
       <c r="G80">
-        <v>-7.104680168859747</v>
+        <v>-8.182676560084927</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.021041718832826</v>
       </c>
       <c r="E81">
-        <v>-9.018956195123963</v>
+        <v>-14.29448803136569</v>
       </c>
       <c r="F81">
-        <v>-3.39862799659168</v>
+        <v>-3.63820706821457</v>
       </c>
       <c r="G81">
-        <v>-6.451466496869531</v>
+        <v>-7.627587457878709</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.7128834993375283</v>
       </c>
       <c r="E82">
-        <v>-10.49677840278711</v>
+        <v>-14.04817527314048</v>
       </c>
       <c r="F82">
-        <v>-3.455773648991439</v>
+        <v>-3.369942331345325</v>
       </c>
       <c r="G82">
-        <v>-5.402983619126953</v>
+        <v>-8.148720294488623</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.4985921445031047</v>
       </c>
       <c r="E83">
-        <v>-10.28007733609806</v>
+        <v>-14.13292566419404</v>
       </c>
       <c r="F83">
-        <v>-3.200509553982036</v>
+        <v>-3.749253359593354</v>
       </c>
       <c r="G83">
-        <v>-6.016483986828072</v>
+        <v>-8.711129012882168</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.3747893903467087</v>
       </c>
       <c r="E84">
-        <v>-12.00329755023686</v>
+        <v>-15.30223652313662</v>
       </c>
       <c r="F84">
-        <v>-3.540614358587446</v>
+        <v>-3.641732397582339</v>
       </c>
       <c r="G84">
-        <v>-5.868608538679906</v>
+        <v>-9.160075404008273</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.3399126302628818</v>
       </c>
       <c r="E85">
-        <v>-13.77792500131073</v>
+        <v>-16.13394964480738</v>
       </c>
       <c r="F85">
-        <v>-3.543023967137787</v>
+        <v>-3.519418830468162</v>
       </c>
       <c r="G85">
-        <v>-5.916704144274438</v>
+        <v>-7.506229479500106</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.3920408118034642</v>
       </c>
       <c r="E86">
-        <v>-13.67895067339909</v>
+        <v>-16.75499815564132</v>
       </c>
       <c r="F86">
-        <v>-3.696938802088642</v>
+        <v>-3.625972148164843</v>
       </c>
       <c r="G86">
-        <v>-5.596971656091627</v>
+        <v>-7.746704196927226</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.5243237854556514</v>
       </c>
       <c r="E87">
-        <v>-13.92620082574388</v>
+        <v>-18.30649410693525</v>
       </c>
       <c r="F87">
-        <v>-4.045853762701642</v>
+        <v>-3.364096872811438</v>
       </c>
       <c r="G87">
-        <v>-6.221380271344644</v>
+        <v>-7.593919209744321</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.7382763557888723</v>
       </c>
       <c r="E88">
-        <v>-15.93103778147169</v>
+        <v>-20.42788492667248</v>
       </c>
       <c r="F88">
-        <v>-3.905797146363839</v>
+        <v>-3.82536072291867</v>
       </c>
       <c r="G88">
-        <v>-5.758566004954532</v>
+        <v>-7.569868096401516</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.028167314088579</v>
       </c>
       <c r="E89">
-        <v>-18.22337396652446</v>
+        <v>-22.35989496340893</v>
       </c>
       <c r="F89">
-        <v>-3.91207178920081</v>
+        <v>-3.973716750106333</v>
       </c>
       <c r="G89">
-        <v>-6.078146208042537</v>
+        <v>-7.848063169703091</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.396806133402873</v>
       </c>
       <c r="E90">
-        <v>-19.46578798137287</v>
+        <v>-23.00789695153652</v>
       </c>
       <c r="F90">
-        <v>-3.997576863428344</v>
+        <v>-3.891450354475873</v>
       </c>
       <c r="G90">
-        <v>-6.000278866413339</v>
+        <v>-7.721414939552734</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.842220374995651</v>
       </c>
       <c r="E91">
-        <v>-20.74912128735459</v>
+        <v>-26.34225764812428</v>
       </c>
       <c r="F91">
-        <v>-3.680162605326392</v>
+        <v>-3.500480083278379</v>
       </c>
       <c r="G91">
-        <v>-6.310784864178202</v>
+        <v>-7.246202680118051</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.363104751924717</v>
       </c>
       <c r="E92">
-        <v>-22.29392868253919</v>
+        <v>-26.64693790783435</v>
       </c>
       <c r="F92">
-        <v>-3.901344557182581</v>
+        <v>-3.85325611891322</v>
       </c>
       <c r="G92">
-        <v>-6.867171700235814</v>
+        <v>-7.703018237991003</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.95980561033361</v>
       </c>
       <c r="E93">
-        <v>-24.32369941615323</v>
+        <v>-28.69587314344885</v>
       </c>
       <c r="F93">
-        <v>-3.864600204385513</v>
+        <v>-3.374124898668001</v>
       </c>
       <c r="G93">
-        <v>-6.420075904066161</v>
+        <v>-7.717131093624916</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.62065173827644</v>
       </c>
       <c r="E94">
-        <v>-26.17868916696722</v>
+        <v>-29.81515342155469</v>
       </c>
       <c r="F94">
-        <v>-3.912663303360227</v>
+        <v>-4.01788234882315</v>
       </c>
       <c r="G94">
-        <v>-6.592320277928902</v>
+        <v>-7.406545642767111</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.341296504052138</v>
       </c>
       <c r="E95">
-        <v>-28.79291834143322</v>
+        <v>-31.81005716954667</v>
       </c>
       <c r="F95">
-        <v>-3.889178528340175</v>
+        <v>-3.381424199232261</v>
       </c>
       <c r="G95">
-        <v>-6.811177132984581</v>
+        <v>-8.331670972625366</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.105205468877235</v>
       </c>
       <c r="E96">
-        <v>-31.53169187229517</v>
+        <v>-34.59194630143566</v>
       </c>
       <c r="F96">
-        <v>-4.076240328101179</v>
+        <v>-3.552655274662532</v>
       </c>
       <c r="G96">
-        <v>-7.429544002628428</v>
+        <v>-8.149855811608592</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.890550942717035</v>
       </c>
       <c r="E97">
-        <v>-33.97354241942219</v>
+        <v>-37.44967605176809</v>
       </c>
       <c r="F97">
-        <v>-3.510771004316905</v>
+        <v>-3.310128926331008</v>
       </c>
       <c r="G97">
-        <v>-7.13900390501091</v>
+        <v>-7.084300450519994</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.682292634656307</v>
       </c>
       <c r="E98">
-        <v>-35.758161948394</v>
+        <v>-38.19514438596277</v>
       </c>
       <c r="F98">
-        <v>-3.501651233802846</v>
+        <v>-3.448652515342665</v>
       </c>
       <c r="G98">
-        <v>-6.728900144697074</v>
+        <v>-9.153791988574737</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.43759634444598</v>
       </c>
       <c r="E99">
-        <v>-38.51529164864604</v>
+        <v>-39.88622602006914</v>
       </c>
       <c r="F99">
-        <v>-3.24216893808767</v>
+        <v>-3.38147646152747</v>
       </c>
       <c r="G99">
-        <v>-8.013626862667582</v>
+        <v>-8.13387249774499</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.160714386508516</v>
       </c>
       <c r="E100">
-        <v>-39.57233937270147</v>
+        <v>-41.8018905298749</v>
       </c>
       <c r="F100">
-        <v>-3.075652555167663</v>
+        <v>-3.4759975735316</v>
       </c>
       <c r="G100">
-        <v>-8.455448959793177</v>
+        <v>-9.266866982014083</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.779271023489153</v>
       </c>
       <c r="E101">
-        <v>-42.58563579061941</v>
+        <v>-46.07712094985131</v>
       </c>
       <c r="F101">
-        <v>-2.811443689147857</v>
+        <v>-2.259442992321438</v>
       </c>
       <c r="G101">
-        <v>-7.300899513517889</v>
+        <v>-8.153702665525225</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.355983189737463</v>
       </c>
       <c r="E102">
-        <v>-45.61433128440044</v>
+        <v>-48.58082252709359</v>
       </c>
       <c r="F102">
-        <v>-2.792767837140038</v>
+        <v>-2.495155445951784</v>
       </c>
       <c r="G102">
-        <v>-8.212706518671656</v>
+        <v>-9.083125083493455</v>
       </c>
     </row>
   </sheetData>
